--- a/ig/main/ValueSet-jdv-j380-categorie-entite-geographique-exercice-rass.xlsx
+++ b/ig/main/ValueSet-jdv-j380-categorie-entite-geographique-exercice-rass.xlsx
@@ -48,43 +48,43 @@
     <t>Title</t>
   </si>
   <si>
+    <t>Jdv J380 Categorie Entite Geographique Exercice Rass</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2026-02-23T18:02:28.249+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
     <t>Ce JDV remplace le JDV-J129-CategorieEtablissement-RASS</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2026-02-23T18:02:28.249+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Catégories d'établissements FINESS</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/main/ValueSet-jdv-j380-categorie-entite-geographique-exercice-rass.xlsx
+++ b/ig/main/ValueSet-jdv-j380-categorie-entite-geographique-exercice-rass.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t/>
@@ -381,7 +387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -415,15 +421,26 @@
         <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-jdv-j380-categorie-entite-geographique-exercice-rass.xlsx
+++ b/ig/main/ValueSet-jdv-j380-categorie-entite-geographique-exercice-rass.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="364">
   <si>
     <t>Property</t>
   </si>
@@ -66,15 +67,12 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T18:02:28.249+00:00</t>
+    <t>2026-05-29T09:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
-  </si>
-  <si>
     <t>Jurisdiction</t>
   </si>
   <si>
@@ -84,9 +82,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce JDV remplace le JDV-J129-CategorieEtablissement-RASS</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -99,31 +94,1018 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>rass</t>
-  </si>
-  <si>
-    <t>=</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice|20260505120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice</t>
+  </si>
+  <si>
+    <t>641</t>
+  </si>
+  <si>
+    <t>Antenne de Pharmacie d'officine</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>Appartement Thérapeutique</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>Atelier Thérapeutique</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Autre Centre d'Accueil</t>
+  </si>
+  <si>
+    <t>698</t>
+  </si>
+  <si>
+    <t>Autre Etablissement Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>612</t>
+  </si>
+  <si>
+    <t>Autre Laboratoire de Biologie Médicale sans FSE</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>Autres résidences sociales</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
+  </si>
+  <si>
+    <t>443</t>
+  </si>
+  <si>
+    <t>Centre Accueil Demandeurs Asile (C.A.D.A.)</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>Centre Crise Accueil Permanent</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Thérapeutique à temps partiel (C.A.T.T.P.)</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>Centre d'Examens de Santé</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>Centre de Consultations Cancer</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Centre de dialyse</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>Centre de Jour pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>637</t>
+  </si>
+  <si>
+    <t>Centre de Lutte Antituberculeuse (CLAT)</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Centre de Lutte Contre Cancer</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>Centre de Médecine collective</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Sportive</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Universitaire</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Centre de Santé</t>
+  </si>
+  <si>
+    <t>649</t>
+  </si>
+  <si>
+    <t>Centre de santé et de médiation en santé sexuelle</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>Centre de Santé Sexuelle</t>
+  </si>
+  <si>
+    <t>636</t>
+  </si>
+  <si>
+    <t>Centre de soins et de prévention</t>
+  </si>
+  <si>
+    <t>645</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination BCG</t>
+  </si>
+  <si>
+    <t>646</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination Internationale</t>
+  </si>
+  <si>
+    <t>638</t>
+  </si>
+  <si>
+    <t>Centre gratuit d'information de dépistage et de diagnostic (CeGIDD)</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier (C.H.)</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Régional (C.H.R.)</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Centre hospitalier, ex Hôpital local</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psychologique (C.M.P.)</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>Centre Médico-Scolaire</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Centre Parents-Enfants de moins de 3 ans</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>Centre Postcure Malades Mentaux</t>
+  </si>
+  <si>
+    <t>442</t>
+  </si>
+  <si>
+    <t>Centre Provisoire Hébergement (C.P.H.)</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
+  </si>
+  <si>
+    <t>461</t>
+  </si>
+  <si>
+    <t>Centres de Ressources S.A.I. (Sans Aucune Indication)</t>
+  </si>
+  <si>
+    <t>463</t>
+  </si>
+  <si>
+    <t>Centres Locaux Information Coordination P.A.(C.L.I.C.)</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>Communauté Professionnelle Territoriale de Santé (CPTS)</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Dispensaire Antihansénien</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Dispensaire Antituberculeux</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Dispensaire Antivénérien</t>
+  </si>
+  <si>
+    <t>606</t>
+  </si>
+  <si>
+    <t>Dispositif d'appui à la coordination (DAC)</t>
+  </si>
+  <si>
+    <t>614</t>
+  </si>
+  <si>
+    <t>Dispositif Spécifique Régional du Cancer (DSRC)</t>
+  </si>
+  <si>
+    <t>650</t>
+  </si>
+  <si>
+    <t>Dispositifs Spécifiques Régionaux en périnatalité</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>Ecole Nationale Santé Publique (E.N.S.P.)</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sanitaires</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sanitaires et Sociales</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sociales</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>EHPA ne percevant pas des crédits d'assurance maladie</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>EHPA percevant des crédits d'assurance maladie</t>
+  </si>
+  <si>
+    <t>699</t>
+  </si>
+  <si>
+    <t>Entité Ayant Autorisation</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Entreprise adaptée</t>
+  </si>
+  <si>
+    <t>647</t>
+  </si>
+  <si>
+    <t>Equipe de Soins Spécialisés</t>
+  </si>
+  <si>
+    <t>608</t>
+  </si>
+  <si>
+    <t>Equipe mobile médico-sociale précarité (EMMSP)</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
+  </si>
+  <si>
+    <t>644</t>
+  </si>
+  <si>
+    <t>Etab. de mise à l'abri pour les pers. se déclarant mineures non accompagnées</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>Etab.Acc.Médicalisé en tout ou partie personnes handicapées</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>Etab.Accueil Non Médicalisé pour personnes handicapées</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Etablissement Consultation Protection Infantile</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>Etablissement d'hébergement pour personnes âgées dépendantes</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>Etablissement de Consultation Pré et Post-natale</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Etablissement de santé privé autorisé en SSR</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Chirurgicaux</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins du Service de Santé des Armées</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Longue Durée</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Pluridisciplinaire</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Etablissement de Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Autres Adultes</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Enfance Protégée</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour personnes handicapées</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>Etablissement Sanitaire des Prisons</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Etablissement Thermal</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>Foyer de l'Enfance</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>Foyers de jeunes travailleurs</t>
+  </si>
+  <si>
+    <t>697</t>
+  </si>
+  <si>
+    <t>Groupement de coopération sanitaire - Etablissement de santé</t>
+  </si>
+  <si>
+    <t>696</t>
+  </si>
+  <si>
+    <t>Groupement de coopération sanitaire de moyens</t>
+  </si>
+  <si>
+    <t>695</t>
+  </si>
+  <si>
+    <t>Groupement de coopération sanitaire de moyens - Exploitant</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>Groupement Régional d'Appui au Développement de la e-Santé (GRADeS)</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Hospitalisation à Domicile</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Hôpital des armées</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>Installation autonome de chirurgie esthétique</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>Institut d'éducation motrice</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>Institut Médico-Educatif (I.M.E.)</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Auditifs</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Visuels</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>Intermédiaire de Placement Social</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>Jardin d'Enfants Spécialisé</t>
+  </si>
+  <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>Laboratoire d'Analyses</t>
+  </si>
+  <si>
+    <t>611</t>
+  </si>
+  <si>
+    <t>Laboratoire de Biologie Médicale</t>
+  </si>
+  <si>
+    <t>624</t>
+  </si>
+  <si>
+    <t>Laboratoire pharmaceutique préparant délivrant allergènes</t>
+  </si>
+  <si>
+    <t>617</t>
+  </si>
+  <si>
+    <t>Lieu de soins non programmés</t>
+  </si>
+  <si>
+    <t>462</t>
+  </si>
+  <si>
+    <t>Lieux de Vie et d’Accueil</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>Maison d'accueil Hospitalière</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Social</t>
+  </si>
+  <si>
+    <t>603</t>
+  </si>
+  <si>
+    <t>Maison de santé (L.6223-3)</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Maison de Santé pour Maladies Mentales</t>
+  </si>
+  <si>
+    <t>609</t>
+  </si>
+  <si>
+    <t>Maison Départementale pour Personnes Handicapées (MDPH)</t>
+  </si>
+  <si>
+    <t>631</t>
+  </si>
+  <si>
+    <t>Maisons de naissance</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>Maisons Relais - Pensions de Famille</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>Pharmacie d'Officine</t>
+  </si>
+  <si>
+    <t>628</t>
+  </si>
+  <si>
+    <t>Pharmacie Minière</t>
+  </si>
+  <si>
+    <t>629</t>
+  </si>
+  <si>
+    <t>Pharmacie Mutualiste</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Social</t>
+  </si>
+  <si>
+    <t>627</t>
+  </si>
+  <si>
+    <t>Propharmacie</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Protection Maternelle et Infantile (P.M.I.)</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Résidences autonomie</t>
+  </si>
+  <si>
+    <t>643</t>
+  </si>
+  <si>
+    <t>Serv. d'éval de la minorité de l'isolement pour les pers. se déclarant mineures</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>Service AEMO et AED</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>Service autonomie aide (SAA)</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Service autonomie aide et soins (SAAS)</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>Service d'accompagnement médico-social adultes handicapés</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>Service d'Accompagnement à la Vie Sociale (S.A.V.S.)</t>
+  </si>
+  <si>
+    <t>640</t>
+  </si>
+  <si>
+    <t>Service d'aide et d'accompagnement à domicile aux familles (SAADF)</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>Service d'information et de soutien aux tuteurs familiaux</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Service de placement familial</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>Service de prévention spécialisée</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Service dédié mesures d'accompagnement social personnalisé</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>Service délégué aux prestations familiales</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d’Activité de Jour</t>
+  </si>
+  <si>
+    <t>441</t>
+  </si>
+  <si>
+    <t>Service d’Intervention Educative en Milieu Ouvert</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>Service d’Investigation Educative</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>Service mandataire judiciaire à la protection des majeurs</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
+  </si>
+  <si>
+    <t>616</t>
+  </si>
+  <si>
+    <t>Services de Prévention et de Santé au Travail (SPST)</t>
+  </si>
+  <si>
+    <t>642</t>
+  </si>
+  <si>
+    <t>Services départementaux d'incendie et de secours</t>
+  </si>
+  <si>
+    <t>639</t>
+  </si>
+  <si>
+    <t>Sociétés de téléconsultation (STLC)</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Structure d'Alternative à la dialyse en centre</t>
+  </si>
+  <si>
+    <t>632</t>
+  </si>
+  <si>
+    <t>Structure Dispensatrice à domicile d'Oxygène à usage médical</t>
+  </si>
+  <si>
+    <t>633</t>
+  </si>
+  <si>
+    <t>Structure Expérimentale en Santé</t>
+  </si>
+  <si>
+    <t>648</t>
+  </si>
+  <si>
+    <t>Structure qui contribue au Service d'Accès aux Soins</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>Syndicat Inter Hospitalier (S.I.H.)</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>Traitements Spécialisés à Domicile</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>Unités Evaluation Réentraînement et d'Orient. Soc. et Pro.</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Village d'Enfants</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Préorientation</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Réadaptation Professionnelle</t>
   </si>
 </sst>
 </file>
@@ -340,44 +1322,40 @@
       <c r="A10" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -387,60 +1365,3487 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G164"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>32</v>
       </c>
+      <c r="E1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>36</v>
+      </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="F77" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="E78" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="E79" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="F79" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="E80" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="F80" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="E81" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="F81" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="E83" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="F83" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="E84" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E85" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="F85" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="E86" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="E87" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="E88" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="F88" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="E89" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="F89" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="E90" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="F90" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="E91" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="F91" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="E92" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="F92" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="E93" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F93" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E94" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="F94" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="E95" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="F95" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="E96" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="F96" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E97" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="F97" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="E98" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="F98" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="E99" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="F99" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="E100" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="F100" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="E101" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="F101" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="F102" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="E103" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="F103" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="E104" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="F104" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="E105" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="F105" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="E106" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="F106" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="E107" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="F107" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="E108" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="F108" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="E109" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="F109" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="E110" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="F110" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="E111" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="F111" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="E112" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="F112" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="E113" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="F113" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="E114" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="F114" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="E115" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="F115" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E116" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="F116" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="E117" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="F117" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="E118" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="F118" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="E119" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="F119" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="E120" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="F120" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="E121" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="F121" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="E122" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="F122" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="E123" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="F123" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="E124" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="F124" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="E125" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="F125" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="E126" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="F126" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E127" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="F127" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="E128" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="F128" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="E129" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="F129" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="E130" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="F130" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="E131" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="F131" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="E132" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="F132" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="E133" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="F133" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="E134" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="F134" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="E135" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="F135" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="E136" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="F136" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="E137" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="F137" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="E138" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="F138" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="E139" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="F139" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="E140" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="F140" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="E141" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="F141" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="E142" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="F142" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="E143" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="F143" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="E144" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="F144" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="E145" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="F145" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="E146" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="F146" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="E147" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="F147" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="E148" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="F148" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="E149" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="F149" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="E150" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="F150" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="E151" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="F151" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="E152" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="F152" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="E153" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="F153" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="E154" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="F154" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="E155" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="F155" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="E156" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="F156" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="E157" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="F157" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="E158" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="F158" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="E159" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="F159" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="E160" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="F160" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="E161" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="F161" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="E162" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="F162" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C163" s="2"/>
+      <c r="D163" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="E163" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="F163" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G163" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C164" s="2"/>
+      <c r="D164" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="E164" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="F164" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
